--- a/presets-source/LSA/Lesson 6/Lesson 6 - Vocab 6.xlsx
+++ b/presets-source/LSA/Lesson 6/Lesson 6 - Vocab 6.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksh12\Projects\vocab-study\presets-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksh12\Projects\vocab-study\presets-source\LSA\Lesson 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,7 +19,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <x:si>
+    <x:t>n. something that is not correct</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑자기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. a large piece of paper with writing or a picture on it.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>She learned not to have too many expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼란스러운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adj. unable to understand or think clearly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"A mistake that ruined my whole day," Emma thought.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adv. happening very quickly in an unexpected way</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현수막</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깨닫다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>downstairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>망치다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>suddenly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>confused</x:t>
+  </x:si>
+  <x:si>
+    <x:t>realize - realized</x:t>
+  </x:si>
+  <x:si>
+    <x:t>banner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>She slowly realized that today was her birthday, not yesterday!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>She saw all the banners, balloons, and ribbons.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emma started to imagine a beautiful party with nice snacks and lots of games to play.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to understand something</x:t>
+  </x:si>
+  <x:si>
+    <x:t>imagine - imagined</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. a belief that something will happen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suddenly, the door opened and Dad, Mom, and Michael jumped into her room.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ruin - ruined</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. something that is added to make it more attractive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>She imagined beautiful decorations and all her friends.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한글 뜻</x:t>
+  </x:si>
   <x:si>
     <x:t>영어 뜻</x:t>
   </x:si>
@@ -30,7 +117,40 @@
     <x:t>영어 단어</x:t>
   </x:si>
   <x:si>
-    <x:t>한글 뜻</x:t>
+    <x:t>장식품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>She walked downstairs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to spoil or destroy something</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emma sat up in her bed and looked confused.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>to make a picture in your mind</x:t>
+  </x:si>
+  <x:si>
+    <x:t>decoration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상상하다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아래층으로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mistake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adv.on or to a lower floor of a building</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expectation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"Nothing, just a mistake I made."</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -714,110 +834,190 @@
   <x:sheetData>
     <x:row r="1" spans="2:5" ht="13.199999999999999">
       <x:c r="B1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:5" ht="13.199999999999999">
       <x:c r="A3" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
+      <x:c r="B3" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="13.199999999999999">
       <x:c r="A4" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
+      <x:c r="B4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="13.199999999999999">
       <x:c r="A5" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="1"/>
-      <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
+      <x:c r="B5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:5" ht="13.199999999999999">
       <x:c r="A6" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="1"/>
-      <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
+      <x:c r="B6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:5" ht="13.199999999999999">
       <x:c r="A7" s="1">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="1"/>
-      <x:c r="C7" s="1"/>
-      <x:c r="D7" s="1"/>
-      <x:c r="E7" s="1"/>
+      <x:c r="B7" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:5" ht="13.199999999999999">
       <x:c r="A8" s="1">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="1"/>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
+      <x:c r="B8" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:5" ht="13.199999999999999">
       <x:c r="A9" s="1">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
+      <x:c r="B9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:5" ht="13.199999999999999">
       <x:c r="A10" s="1">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
+      <x:c r="B10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="13.199999999999999">
       <x:c r="A11" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
+      <x:c r="B11" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>